--- a/ABA_mining/outputs/eval/task3/check-out/llama3.2/contrary_v5/EVAL_SUMMARY.xlsx
+++ b/ABA_mining/outputs/eval/task3/check-out/llama3.2/contrary_v5/EVAL_SUMMARY.xlsx
@@ -541,13 +541,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.714286</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.833334</v>
       </c>
       <c r="O2" t="n">
         <v>0.75</v>
@@ -600,13 +600,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.714286</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.833334</v>
       </c>
       <c r="O3" t="n">
         <v>0.75</v>
@@ -659,13 +659,13 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.714286</v>
       </c>
       <c r="M4" t="n">
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.833334</v>
       </c>
       <c r="O4" t="n">
         <v>0.75</v>
@@ -784,13 +784,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.714286</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.833333</v>
       </c>
       <c r="I2" t="n">
         <v>0.75</v>
